--- a/reportes/RESULTADOS_EXPERIMENTO_CONSOLIDADO.xlsx
+++ b/reportes/RESULTADOS_EXPERIMENTO_CONSOLIDADO.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Configuración" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Comparación de Grupos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Estadísticas Detalladas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuración" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparación de Grupos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estadísticas Detalladas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +35,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
     </font>
     <font>
       <b val="1"/>
@@ -74,13 +78,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -451,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -480,7 +485,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Linux 6.17.0-20-generic</t>
+          <t>Windows 10</t>
         </is>
       </c>
     </row>
@@ -492,7 +497,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>x86_64</t>
+          <t>AMD64</t>
         </is>
       </c>
     </row>
@@ -504,7 +509,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>x86_64</t>
+          <t>AMD Ryzen 7 3700X, 8 nucleos, 3,6 GHz (AMD64 Family 23 Model 113 Stepping 0, AuthenticAMD)</t>
         </is>
       </c>
     </row>
@@ -516,33 +521,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+          <t>32 GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Datos de la maquina del experimento (fijos). No se detecta el equipo donde corre el script.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>GRUPOS EXPERIMENTALES</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Grupo 0 - 0% (Sin CPLEX)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>5 ejecuciones</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Grupo 1 - 10%</t>
+          <t>Grupo 0 - 0% (Sin CPLEX)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -554,7 +554,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Grupo 2 - 25%</t>
+          <t>Grupo 1 - 10%</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -566,7 +566,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Grupo 3 - 50%</t>
+          <t>Grupo 2 - 25%</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -578,7 +578,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Grupo 4 - 75%</t>
+          <t>Grupo 3 - 50%</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -590,10 +590,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Grupo 4 - 75%</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>5 ejecuciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Grupo 5 - 100%</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>5 ejecuciones</t>
         </is>
@@ -634,224 +646,224 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Grupo</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Presupuesto</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Ejecuciones</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Individuos Evaluados (Promedio)</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Llamadas CPLEX (Promedio)</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>Tiempo CPLEX Total (Promedio, s)</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Fitness ERP (Promedio)</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Fitness ERP (Mejor)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Grupo 0</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>0% (Sin CPLEX)</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D4" s="5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="6" t="n">
+      <c r="D4" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="7" t="n">
         <v>0.062614</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H4" s="7" t="n">
         <v>0.02164</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Grupo 1</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="5" t="n">
-        <v>8722.799999999999</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>186211.2</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>234830.4374</v>
-      </c>
-      <c r="G5" s="6" t="n">
+      <c r="D5" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>62845.2</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>78338.47659999999</v>
+      </c>
+      <c r="G5" s="7" t="n">
         <v>0.010228</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="7" t="n">
         <v>0.006911</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Grupo 2</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="5" t="n">
-        <v>8771.4</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>183027.2</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>433895.722</v>
-      </c>
-      <c r="G6" s="6" t="n">
+      <c r="D6" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>64943.2</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>156490.2168</v>
+      </c>
+      <c r="G6" s="7" t="n">
         <v>0.007188</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="7" t="n">
         <v>0.00481</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D7" s="5" t="n">
-        <v>8927</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>244360.4</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>843770.4502</v>
-      </c>
-      <c r="G7" s="6" t="n">
+      <c r="D7" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>82402</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>285610.2122</v>
+      </c>
+      <c r="G7" s="7" t="n">
         <v>0.006013</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="7" t="n">
         <v>0.003109</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Grupo 4</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="5" t="n">
-        <v>9117.799999999999</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>291588.4</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>1677316.7316</v>
-      </c>
-      <c r="G8" s="6" t="n">
+      <c r="D8" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>100053.4</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>558951.7172</v>
+      </c>
+      <c r="G8" s="7" t="n">
         <v>0.001777</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="7" t="n">
         <v>0.001074</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Grupo 5</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="5" t="n">
-        <v>8707</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>261528.8</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>1832586.8406</v>
-      </c>
-      <c r="G9" s="6" t="n">
+      <c r="D9" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>97062</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>674840.956</v>
+      </c>
+      <c r="G9" s="7" t="n">
         <v>0.001176</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H9" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -891,979 +903,979 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Grupo</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Ejecución</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Individuos Evaluados</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Llamadas CPLEX (Total)</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Tiempo Total CPLEX (s)</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>Promedio Llamadas/Indiv</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Promedio Tiempo/Indiv (s)</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Fitness ERP Final</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>Mejor Fitness ERP</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Grupo 0</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="6" t="n">
+      <c r="C4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="7" t="n">
         <v>0.02164</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="7" t="n">
         <v>0.02164</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Grupo 0</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="6" t="n">
+      <c r="C5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7" t="n">
         <v>0.026433</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="7" t="n">
         <v>0.026433</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Grupo 0</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="6" t="n">
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7" t="n">
         <v>0.1249934</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="7" t="n">
         <v>0.1249934</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Grupo 0</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="6" t="n">
+      <c r="C7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7" t="n">
         <v>0.1183645</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" s="7" t="n">
         <v>0.1183645</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Grupo 0</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="6" t="n">
+      <c r="C8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7" t="n">
         <v>0.02164</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="7" t="n">
         <v>0.02164</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Grupo 1</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="5" t="n">
-        <v>2983</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>64818</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>80711.82799999999</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>21.73</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>27.057</v>
-      </c>
-      <c r="H9" s="6" t="n">
+      <c r="C9" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>64927</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>80715.158</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>12.985</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>16.143</v>
+      </c>
+      <c r="H9" s="7" t="n">
         <v>0.0143313</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="I9" s="7" t="n">
         <v>0.0143313</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Grupo 1</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="5" t="n">
-        <v>5786</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>116599</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>161413.109</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>20.15</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>27.897</v>
-      </c>
-      <c r="H10" s="6" t="n">
+      <c r="C10" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>51817</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>80704.67999999999</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>10.363</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>16.141</v>
+      </c>
+      <c r="H10" s="7" t="n">
         <v>0.0069106</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="I10" s="7" t="n">
         <v>0.0069106</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Grupo 1</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>8717</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>178329</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>228913.109</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>20.46</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>26.261</v>
-      </c>
-      <c r="H11" s="6" t="n">
+      <c r="C11" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>61898</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>67502.973</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>13.501</v>
+      </c>
+      <c r="H11" s="7" t="n">
         <v>0.0073188</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="7" t="n">
         <v>0.0073188</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Grupo 1</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="5" t="n">
-        <v>11641</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>257654</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>311438</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>22.13</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>26.754</v>
-      </c>
-      <c r="H12" s="6" t="n">
+      <c r="C12" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>79536</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>82528.209</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>15.907</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>16.506</v>
+      </c>
+      <c r="H12" s="7" t="n">
         <v>0.008400400000000001</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" s="7" t="n">
         <v>0.008400400000000001</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Grupo 1</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C13" s="5" t="n">
-        <v>14487</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>313656</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>391676.141</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>27.036</v>
-      </c>
-      <c r="H13" s="6" t="n">
+      <c r="C13" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>56048</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>80241.363</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>16.048</v>
+      </c>
+      <c r="H13" s="7" t="n">
         <v>0.0141765</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="I13" s="7" t="n">
         <v>0.0141765</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Grupo 2</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="5" t="n">
-        <v>2843</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>47303</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>108317.625</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>16.64</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="H14" s="6" t="n">
+      <c r="C14" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>47326</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>108319.931</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>9.465</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>21.664</v>
+      </c>
+      <c r="H14" s="7" t="n">
         <v>0.0048098</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="I14" s="7" t="n">
         <v>0.0048098</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Grupo 2</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="5" t="n">
-        <v>5891</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>115866</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>274242.531</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>19.67</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>46.553</v>
-      </c>
-      <c r="H15" s="6" t="n">
+      <c r="C15" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>68616</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>165928.204</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>13.723</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>33.186</v>
+      </c>
+      <c r="H15" s="7" t="n">
         <v>0.0082249</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I15" s="7" t="n">
         <v>0.0082249</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Grupo 2</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="5" t="n">
-        <v>8781</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>180049</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>414356.375</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>47.188</v>
-      </c>
-      <c r="H16" s="6" t="n">
+      <c r="C16" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>64283</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>140116.704</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>12.857</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>28.023</v>
+      </c>
+      <c r="H16" s="7" t="n">
         <v>0.0070534</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I16" s="7" t="n">
         <v>0.0070534</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Grupo 2</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C17" s="5" t="n">
-        <v>11673</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>247411</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>590126.938</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>50.555</v>
-      </c>
-      <c r="H17" s="6" t="n">
+      <c r="C17" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>67377</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>175774.102</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>13.475</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>35.155</v>
+      </c>
+      <c r="H17" s="7" t="n">
         <v>0.0073188</v>
       </c>
-      <c r="I17" s="6" t="n">
+      <c r="I17" s="7" t="n">
         <v>0.0073188</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Grupo 2</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C18" s="5" t="n">
-        <v>14669</v>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>324507</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>782435.1409999999</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>22.12</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>53.339</v>
-      </c>
-      <c r="H18" s="6" t="n">
+      <c r="C18" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>77114</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>192312.143</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>15.423</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>38.462</v>
+      </c>
+      <c r="H18" s="7" t="n">
         <v>0.0085346</v>
       </c>
-      <c r="I18" s="6" t="n">
+      <c r="I18" s="7" t="n">
         <v>0.0085346</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="5" t="n">
-        <v>2945</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>87291</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>321393.125</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>29.64</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>109.132</v>
-      </c>
-      <c r="H19" s="6" t="n">
+      <c r="C19" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>87325</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>321397.155</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>17.465</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>64.279</v>
+      </c>
+      <c r="H19" s="7" t="n">
         <v>0.0069394</v>
       </c>
-      <c r="I19" s="6" t="n">
+      <c r="I19" s="7" t="n">
         <v>0.0069394</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="5" t="n">
-        <v>5862</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>150837</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>510336.391</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>25.73</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>87.05800000000001</v>
-      </c>
-      <c r="H20" s="6" t="n">
+      <c r="C20" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>63663</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>188945.993</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>12.733</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>37.789</v>
+      </c>
+      <c r="H20" s="7" t="n">
         <v>0.0077362</v>
       </c>
-      <c r="I20" s="6" t="n">
+      <c r="I20" s="7" t="n">
         <v>0.0077362</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="5" t="n">
-        <v>8967</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>240506</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>784805.344</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>26.82</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>87.52200000000001</v>
-      </c>
-      <c r="H21" s="6" t="n">
+      <c r="C21" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>89751</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>274472.784</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>54.895</v>
+      </c>
+      <c r="H21" s="7" t="n">
         <v>0.0058</v>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="I21" s="7" t="n">
         <v>0.0058</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C22" s="5" t="n">
-        <v>11946</v>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>331511</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>1174285.047</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>27.75</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>98.29900000000001</v>
-      </c>
-      <c r="H22" s="6" t="n">
+      <c r="C22" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>91042</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>389484.142</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>18.208</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>77.89700000000001</v>
+      </c>
+      <c r="H22" s="7" t="n">
         <v>0.0031093</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I22" s="7" t="n">
         <v>0.0031093</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="B23" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C23" s="5" t="n">
-        <v>14915</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>411657</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>1428032.344</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>95.745</v>
-      </c>
-      <c r="H23" s="6" t="n">
+      <c r="C23" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>80229</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>253750.987</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>16.046</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>50.75</v>
+      </c>
+      <c r="H23" s="7" t="n">
         <v>0.006478</v>
       </c>
-      <c r="I23" s="6" t="n">
+      <c r="I23" s="7" t="n">
         <v>0.006478</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>Grupo 4</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n">
+      <c r="B24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C24" s="5" t="n">
-        <v>3241</v>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>89915</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>562767.563</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>27.74</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>173.64</v>
-      </c>
-      <c r="H24" s="6" t="n">
+      <c r="C24" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>89925</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>562771.733</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>17.985</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>112.554</v>
+      </c>
+      <c r="H24" s="7" t="n">
         <v>0.0014308</v>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="I24" s="7" t="n">
         <v>0.0014308</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Grupo 4</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n">
+      <c r="B25" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C25" s="5" t="n">
-        <v>6092</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>191927</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>1228142.078</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>201.599</v>
-      </c>
-      <c r="H25" s="6" t="n">
+      <c r="C25" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>102055</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>665379.749</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>20.411</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>133.076</v>
+      </c>
+      <c r="H25" s="7" t="n">
         <v>0.0010745</v>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="I25" s="7" t="n">
         <v>0.0010745</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Grupo 4</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n">
+      <c r="B26" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C26" s="5" t="n">
-        <v>9143</v>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>286979</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>1594449.641</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>31.39</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>174.39</v>
-      </c>
-      <c r="H26" s="6" t="n">
+      <c r="C26" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>95245</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>366311.425</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>19.049</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>73.262</v>
+      </c>
+      <c r="H26" s="7" t="n">
         <v>0.0037459</v>
       </c>
-      <c r="I26" s="6" t="n">
+      <c r="I26" s="7" t="n">
         <v>0.0037459</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>Grupo 4</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n">
+      <c r="B27" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C27" s="5" t="n">
-        <v>12142</v>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>389319</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>2206488.063</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>32.06</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>181.724</v>
-      </c>
-      <c r="H27" s="6" t="n">
+      <c r="C27" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>102371</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>612042.943</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>20.474</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>122.409</v>
+      </c>
+      <c r="H27" s="7" t="n">
         <v>0.0010745</v>
       </c>
-      <c r="I27" s="6" t="n">
+      <c r="I27" s="7" t="n">
         <v>0.0010745</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Grupo 4</t>
         </is>
       </c>
-      <c r="B28" s="4" t="n">
+      <c r="B28" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C28" s="5" t="n">
-        <v>14971</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>499802</v>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>2794736.313</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>33.38</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>186.677</v>
-      </c>
-      <c r="H28" s="6" t="n">
+      <c r="C28" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>110671</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>588252.736</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>22.134</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>117.651</v>
+      </c>
+      <c r="H28" s="7" t="n">
         <v>0.0015594</v>
       </c>
-      <c r="I28" s="6" t="n">
+      <c r="I28" s="7" t="n">
         <v>0.0015594</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Grupo 5</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n">
+      <c r="B29" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C29" s="5" t="n">
-        <v>2838</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>69717</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>483533.375</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>24.57</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>170.378</v>
-      </c>
-      <c r="H29" s="6" t="n">
+      <c r="C29" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>69741</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>483536.522</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>13.948</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>96.70699999999999</v>
+      </c>
+      <c r="H29" s="7" t="n">
         <v>0.0012533</v>
       </c>
-      <c r="I29" s="6" t="n">
+      <c r="I29" s="7" t="n">
         <v>0.0012533</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Grupo 5</t>
         </is>
       </c>
-      <c r="B30" s="4" t="n">
+      <c r="B30" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C30" s="5" t="n">
-        <v>5792</v>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>156225</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>1161239.516</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>26.97</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>200.49</v>
-      </c>
-      <c r="H30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="6" t="n">
+      <c r="C30" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>86515</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>677710.1629999999</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>17.303</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>135.542</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Grupo 5</t>
         </is>
       </c>
-      <c r="B31" s="4" t="n">
+      <c r="B31" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C31" s="5" t="n">
-        <v>8716</v>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>239337</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>1704126.781</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>27.46</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>195.517</v>
-      </c>
-      <c r="H31" s="6" t="n">
+      <c r="C31" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>83181</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>542891.126</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>16.636</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>108.578</v>
+      </c>
+      <c r="H31" s="7" t="n">
         <v>0.0019538</v>
       </c>
-      <c r="I31" s="6" t="n">
+      <c r="I31" s="7" t="n">
         <v>0.0019538</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>Grupo 5</t>
         </is>
       </c>
-      <c r="B32" s="4" t="n">
+      <c r="B32" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C32" s="5" t="n">
-        <v>11675</v>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>357541</v>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>2439849.359</v>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>30.62</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>208.981</v>
-      </c>
-      <c r="H32" s="6" t="n">
+      <c r="C32" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>118398</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>735726.9</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>147.145</v>
+      </c>
+      <c r="H32" s="7" t="n">
         <v>0.0014863</v>
       </c>
-      <c r="I32" s="6" t="n">
+      <c r="I32" s="7" t="n">
         <v>0.0014863</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>Grupo 5</t>
         </is>
       </c>
-      <c r="B33" s="4" t="n">
+      <c r="B33" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C33" s="5" t="n">
-        <v>14514</v>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>484824</v>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>3374185.172</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>232.478</v>
-      </c>
-      <c r="H33" s="6" t="n">
+      <c r="C33" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>127475</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>934340.069</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>25.495</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>186.868</v>
+      </c>
+      <c r="H33" s="7" t="n">
         <v>0.0011857</v>
       </c>
-      <c r="I33" s="6" t="n">
+      <c r="I33" s="7" t="n">
         <v>0.0011857</v>
       </c>
     </row>
